--- a/data/trans_dic/P1422-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1422-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,66</t>
+          <t>1,46; 3,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,1</t>
+          <t>0,6; 2,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,06</t>
+          <t>1,66; 3,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,06</t>
+          <t>0,8; 2,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,08</t>
+          <t>0,56; 2,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,76</t>
+          <t>1,99; 3,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,49</t>
+          <t>1,23; 2,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,73</t>
+          <t>0,68; 1,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,53</t>
+          <t>2,05; 3,42</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -793,42 +793,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,8</t>
+          <t>0,15; 0,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,47</t>
+          <t>0,77; 1,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,79</t>
+          <t>0,17; 0,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,76</t>
+          <t>0,11; 0,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,85</t>
+          <t>0,43; 0,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,73</t>
+          <t>0,28; 0,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,6</t>
+          <t>0,18; 0,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,05</t>
+          <t>0,65; 1,16</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,99</t>
+          <t>0,34; 2,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,51</t>
+          <t>0,22; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,55</t>
+          <t>0,35; 1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,93</t>
+          <t>0,24; 0,9</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,38</t>
+          <t>0,68; 1,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,95</t>
+          <t>0,41; 0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,57</t>
+          <t>0,97; 1,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,04</t>
+          <t>0,47; 1,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,94</t>
+          <t>0,35; 0,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,25</t>
+          <t>0,77; 1,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,08</t>
+          <t>0,64; 1,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,85</t>
+          <t>0,44; 0,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,32</t>
+          <t>0,97; 1,39</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>37174</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14062; 35625</t>
+          <t>14190; 36937</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4324; 15855</t>
+          <t>4555; 15912</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9133; 20841</t>
+          <t>9567; 22700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10541; 27563</t>
+          <t>10643; 28572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5528; 20673</t>
+          <t>5570; 20475</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14794; 28265</t>
+          <t>16303; 30202</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29650; 57528</t>
+          <t>28532; 56078</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12428; 30263</t>
+          <t>11838; 31147</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26141; 44675</t>
+          <t>28675; 47775</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>39268</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5875; 18847</t>
+          <t>5954; 18919</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3284; 16564</t>
+          <t>3068; 16067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14746; 33668</t>
+          <t>17133; 35963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2367; 13776</t>
+          <t>3026; 14096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3090; 15123</t>
+          <t>2173; 13185</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7326; 19013</t>
+          <t>9253; 21359</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10390; 27079</t>
+          <t>10586; 27560</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8167; 24492</t>
+          <t>7511; 23818</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25104; 47668</t>
+          <t>28707; 50821</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>7058</t>
         </is>
       </c>
     </row>
@@ -1637,42 +1637,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1820; 10890</t>
+          <t>1850; 11544</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1414; 9766</t>
+          <t>1561; 10934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 5576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 10986</t>
+          <t>0; 11127</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>514; 4856</t>
+          <t>715; 5956</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5556</t>
+          <t>0; 6489</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3567; 16989</t>
+          <t>3836; 17493</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2634; 12122</t>
+          <t>3418; 13031</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22578; 47206</t>
+          <t>23262; 46752</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14337; 32140</t>
+          <t>13788; 31396</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30337; 54097</t>
+          <t>33957; 58067</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17128; 36810</t>
+          <t>16752; 38760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12527; 33115</t>
+          <t>12309; 32654</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26465; 45457</t>
+          <t>28846; 48212</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45010; 75456</t>
+          <t>44618; 75572</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30361; 58589</t>
+          <t>30199; 58006</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61261; 93599</t>
+          <t>69946; 100900</t>
         </is>
       </c>
     </row>
